--- a/data/trans_dic/IP31KM06_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM06_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,29; 23,84</t>
+          <t>19,03; 39,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,47; 36,8</t>
+          <t>10,93; 26,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,24; 27,5</t>
+          <t>17,23; 29,87</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>46,76%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,87; 80,94</t>
+          <t>40,65; 58,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39,88; 58,51</t>
+          <t>34,17; 52,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,75; 66,48</t>
+          <t>39,87; 53,14</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,63%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,8; 43,76</t>
+          <t>20,35; 39,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,33; 40,55</t>
+          <t>23,36; 43,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,06; 38,35</t>
+          <t>24,99; 38,29</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,83%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,05; 39,97</t>
+          <t>15,15; 55,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,85; 61,07</t>
+          <t>21,46; 40,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,38; 49,65</t>
+          <t>22,02; 44,78</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,21; 16,87</t>
+          <t>14,42; 35,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,15; 33,86</t>
+          <t>2,95; 16,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,08; 24,18</t>
+          <t>10,55; 23,27</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,41; 35,18</t>
+          <t>13,45; 31,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,26; 32,12</t>
+          <t>16,57; 36,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,55; 29,78</t>
+          <t>16,65; 30,58</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,56%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>25,7; 40,23</t>
+          <t>29,46; 46,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,35; 47,41</t>
+          <t>27,59; 41,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30,71; 41,91</t>
+          <t>31,3; 41,92</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>51,24%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>45,31%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>51,39%</t>
-        </is>
-      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,46%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>37,81; 53,0</t>
+          <t>43,84; 58,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>44,8; 58,33</t>
+          <t>38,05; 53,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43,02; 53,96</t>
+          <t>43,03; 53,87</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,5%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>30,93; 44,02</t>
+          <t>35,12; 42,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>34,22; 42,3</t>
+          <t>30,99; 37,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>34,28; 41,2</t>
+          <t>34,02; 39,28</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10566</t>
+          <t>16659</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19319</t>
+          <t>10009</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29886</t>
+          <t>26668</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6630; 17023</t>
+          <t>11466; 23797</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13035; 27458</t>
+          <t>6005; 14480</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22259; 40157</t>
+          <t>19849; 34410</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>54</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>68675</t>
+          <t>57415</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>62222</t>
+          <t>42786</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>130897</t>
+          <t>100201</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>48835; 101700</t>
+          <t>46731; 67498</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50417; 73971</t>
+          <t>33942; 52052</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>107766; 167582</t>
+          <t>85435; 113873</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18426</t>
+          <t>17046</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19446</t>
+          <t>18199</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37872</t>
+          <t>35245</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13223; 24310</t>
+          <t>11659; 22464</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13788; 26207</t>
+          <t>12643; 23540</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30122; 46090</t>
+          <t>27838; 42657</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>20639</t>
+          <t>20454</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>23154</t>
+          <t>21388</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43793</t>
+          <t>41842</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13974; 27853</t>
+          <t>10574; 38596</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11194; 46023</t>
+          <t>15120; 28782</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31007; 72023</t>
+          <t>30896; 62814</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9445</t>
+          <t>2981</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12239</t>
+          <t>12312</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1099; 5770</t>
+          <t>5706; 13858</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5763; 13787</t>
+          <t>1043; 6008</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8300; 18116</t>
+          <t>7910; 17439</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>10655</t>
+          <t>10144</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>11064</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22104</t>
+          <t>21208</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6824; 15581</t>
+          <t>6348; 14823</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7130; 17276</t>
+          <t>7337; 16025</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16230; 29203</t>
+          <t>15230; 27976</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>57</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>40073</t>
+          <t>53622</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>60070</t>
+          <t>42300</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>100143</t>
+          <t>95921</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>31792; 49763</t>
+          <t>41406; 64723</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>48599; 73509</t>
+          <t>33617; 50551</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>85592; 116833</t>
+          <t>82138; 109984</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>81</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>58303</t>
+          <t>80512</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>79228</t>
+          <t>62476</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>137531</t>
+          <t>142988</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>48654; 68192</t>
+          <t>68894; 91912</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>69067; 89914</t>
+          <t>52465; 73917</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>121661; 152599</t>
+          <t>126954; 158941</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>290</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>230130</t>
+          <t>265182</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>284334</t>
+          <t>211202</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>514464</t>
+          <t>476384</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>202004; 287541</t>
+          <t>241225; 291196</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>254866; 315021</t>
+          <t>191598; 234513</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>479166; 575961</t>
+          <t>444019; 512656</t>
         </is>
       </c>
     </row>
